--- a/Parishes/Input/RawData.xlsx
+++ b/Parishes/Input/RawData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="171">
   <si>
     <t>Timestamp</t>
   </si>
@@ -408,9 +408,6 @@
   </si>
   <si>
     <t>Group Verification &amp; Endorsement</t>
-  </si>
-  <si>
-    <t>jeanettebalatico4@gmail.com</t>
   </si>
   <si>
     <t>Vicariate of St. Vincent Ferrer</t>
@@ -4148,30 +4145,26 @@
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:140">
-      <c r="A2" s="2">
-        <v>46247.8049537037</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="G2" s="4">
         <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -4182,208 +4175,208 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="T2" s="4">
         <v>26</v>
       </c>
       <c r="U2" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="X2" s="4">
         <v>34</v>
       </c>
       <c r="Y2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z2" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="AA2" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="AB2" s="4">
         <v>16</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE2" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="AF2" s="4">
         <v>23</v>
       </c>
       <c r="AG2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="AH2" s="3" t="s">
+      <c r="AI2" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="AJ2" s="4">
         <v>23</v>
       </c>
       <c r="AK2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AL2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM2" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="AM2" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="AN2" s="4">
         <v>21</v>
       </c>
       <c r="AO2" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AP2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="AQ2" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="AR2" s="4">
         <v>20</v>
       </c>
       <c r="AS2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AT2" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="AU2" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="AU2" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="AV2" s="4">
         <v>20</v>
       </c>
       <c r="AW2" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AX2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AY2" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="AY2" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="AZ2" s="4">
         <v>21</v>
       </c>
       <c r="BA2" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BB2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BC2" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="BC2" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="BD2" s="4">
         <v>15</v>
       </c>
       <c r="BE2" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BF2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="BG2" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="BG2" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="BH2" s="4">
         <v>17</v>
       </c>
       <c r="BI2" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BJ2" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="BK2" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="BK2" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="BL2" s="4">
         <v>27</v>
       </c>
       <c r="BM2" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BN2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="BO2" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="BO2" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="BP2" s="4">
         <v>13</v>
       </c>
       <c r="BQ2" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BR2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="BS2" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="BS2" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="BT2" s="4">
         <v>21</v>
       </c>
       <c r="BU2" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BV2" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="BW2" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="BW2" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="BX2" s="4">
         <v>19</v>
       </c>
       <c r="BY2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="BZ2" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="BZ2" s="3" t="s">
+      <c r="CA2" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="CA2" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="CB2" s="4">
         <v>19</v>
       </c>
       <c r="CC2" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="CD2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="CE2" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="CE2" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="CF2" s="4">
         <v>22</v>
       </c>
       <c r="CG2" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="CH2" s="5"/>
       <c r="CI2" s="5"/>
@@ -4435,7 +4428,7 @@
       <c r="EC2" s="5"/>
       <c r="ED2" s="6"/>
       <c r="EE2" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="EF2" s="8"/>
       <c r="EG2" s="8"/>
